--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="467">
   <si>
     <t>Property</t>
   </si>
@@ -1160,6 +1160,10 @@
   </si>
   <si>
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profile:$this.resolve}
+</t>
   </si>
   <si>
     <t>OBXs</t>
@@ -6983,7 +6987,7 @@
         <v>79</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>306</v>
+        <v>359</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -7011,7 +7015,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7019,13 +7023,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>353</v>
@@ -7047,7 +7051,7 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>355</v>
@@ -7126,7 +7130,7 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7134,13 +7138,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>353</v>
@@ -7162,7 +7166,7 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>355</v>
@@ -7241,7 +7245,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7249,13 +7253,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>353</v>
@@ -7277,7 +7281,7 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>355</v>
@@ -7356,7 +7360,7 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7364,13 +7368,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>353</v>
@@ -7392,7 +7396,7 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>355</v>
@@ -7471,7 +7475,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7479,13 +7483,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>353</v>
@@ -7507,7 +7511,7 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>355</v>
@@ -7586,7 +7590,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7594,13 +7598,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>353</v>
@@ -7622,7 +7626,7 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>355</v>
@@ -7701,7 +7705,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7709,13 +7713,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>353</v>
@@ -7737,7 +7741,7 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>355</v>
@@ -7816,7 +7820,7 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -7824,13 +7828,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>353</v>
@@ -7852,7 +7856,7 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>355</v>
@@ -7931,7 +7935,7 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
@@ -7939,13 +7943,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>353</v>
@@ -7967,7 +7971,7 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>355</v>
@@ -8046,7 +8050,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8054,13 +8058,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>353</v>
@@ -8082,7 +8086,7 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>355</v>
@@ -8161,7 +8165,7 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8169,13 +8173,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>353</v>
@@ -8197,7 +8201,7 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>355</v>
@@ -8276,7 +8280,7 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8284,13 +8288,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>353</v>
@@ -8312,7 +8316,7 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>355</v>
@@ -8391,7 +8395,7 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
@@ -8399,13 +8403,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>353</v>
@@ -8427,7 +8431,7 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>355</v>
@@ -8506,7 +8510,7 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
@@ -8514,13 +8518,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>353</v>
@@ -8542,7 +8546,7 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>355</v>
@@ -8621,7 +8625,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -8629,13 +8633,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>353</v>
@@ -8657,7 +8661,7 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>355</v>
@@ -8736,7 +8740,7 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
@@ -8744,13 +8748,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>353</v>
@@ -8772,7 +8776,7 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>355</v>
@@ -8851,7 +8855,7 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -8859,13 +8863,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>353</v>
@@ -8887,7 +8891,7 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>355</v>
@@ -8966,7 +8970,7 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -8974,10 +8978,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9000,16 +9004,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9059,7 +9063,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9085,14 +9089,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9111,17 +9115,17 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9170,7 +9174,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9188,7 +9192,7 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
@@ -9196,10 +9200,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9305,10 +9309,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9416,14 +9420,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9445,10 +9449,10 @@
         <v>108</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>111</v>
@@ -9503,7 +9507,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9529,10 +9533,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9558,16 +9562,16 @@
         <v>102</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -9616,7 +9620,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9642,10 +9646,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9668,13 +9672,13 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9725,7 +9729,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>88</v>
@@ -9751,14 +9755,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9780,14 +9784,14 @@
         <v>102</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -9836,7 +9840,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9854,7 +9858,7 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
@@ -9862,10 +9866,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9891,10 +9895,10 @@
         <v>223</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9924,10 +9928,10 @@
         <v>153</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>79</v>
@@ -9945,7 +9949,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9963,7 +9967,7 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
@@ -9971,10 +9975,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10080,10 +10084,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10191,10 +10195,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10302,13 +10306,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="B76" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="C76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>79</v>
@@ -10352,7 +10356,7 @@
         <v>79</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>79</v>
@@ -10417,10 +10421,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>250</v>
@@ -10467,7 +10471,7 @@
         <v>79</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>79</v>
@@ -10486,7 +10490,7 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>79</v>
@@ -10530,10 +10534,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10643,10 +10647,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10669,19 +10673,19 @@
         <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -10730,7 +10734,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -10748,7 +10752,7 @@
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>79</v>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-bodyplethysmographie.xlsx
@@ -1487,7 +1487,7 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://snomed.info/sct|http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
